--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,464 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122381070</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78645</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Flarmyran, Flarmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>563303</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7041148</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122381405</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78645</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flarmyran, Flarmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563283</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7041083</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122381396</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79726</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flarmyran, Flarmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>563278</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7041093</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122381436</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flarmyran, Flarmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563292</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7041070</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381070</v>
+        <v>122381396</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563303</v>
+        <v>563278</v>
       </c>
       <c r="R3" t="n">
-        <v>7041148</v>
+        <v>7041093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381405</v>
+        <v>122381436</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563283</v>
+        <v>563292</v>
       </c>
       <c r="R4" t="n">
-        <v>7041083</v>
+        <v>7041070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381396</v>
+        <v>122381405</v>
       </c>
       <c r="B5" t="n">
-        <v>79726</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563278</v>
+        <v>563283</v>
       </c>
       <c r="R5" t="n">
-        <v>7041093</v>
+        <v>7041083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381436</v>
+        <v>122381070</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563292</v>
+        <v>563303</v>
       </c>
       <c r="R6" t="n">
-        <v>7041070</v>
+        <v>7041148</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,12 +1223,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381396</v>
+        <v>122381070</v>
       </c>
       <c r="B3" t="n">
-        <v>79727</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563278</v>
+        <v>563303</v>
       </c>
       <c r="R3" t="n">
-        <v>7041093</v>
+        <v>7041148</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381436</v>
+        <v>122381405</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563292</v>
+        <v>563283</v>
       </c>
       <c r="R4" t="n">
-        <v>7041070</v>
+        <v>7041083</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +989,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381405</v>
+        <v>122381396</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563283</v>
+        <v>563278</v>
       </c>
       <c r="R5" t="n">
-        <v>7041083</v>
+        <v>7041093</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381070</v>
+        <v>122381436</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1129,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563303</v>
+        <v>563292</v>
       </c>
       <c r="R6" t="n">
-        <v>7041148</v>
+        <v>7041070</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,12 +1223,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381070</v>
+        <v>122381396</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563303</v>
+        <v>563278</v>
       </c>
       <c r="R3" t="n">
-        <v>7041148</v>
+        <v>7041093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381405</v>
+        <v>122381070</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563283</v>
+        <v>563303</v>
       </c>
       <c r="R4" t="n">
-        <v>7041083</v>
+        <v>7041148</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381396</v>
+        <v>122381405</v>
       </c>
       <c r="B5" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563278</v>
+        <v>563283</v>
       </c>
       <c r="R5" t="n">
-        <v>7041093</v>
+        <v>7041083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
         <v>122381436</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381396</v>
+        <v>122381405</v>
       </c>
       <c r="B3" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563278</v>
+        <v>563283</v>
       </c>
       <c r="R3" t="n">
-        <v>7041093</v>
+        <v>7041083</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381070</v>
+        <v>122381436</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563303</v>
+        <v>563292</v>
       </c>
       <c r="R4" t="n">
-        <v>7041148</v>
+        <v>7041070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,19 +999,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381405</v>
+        <v>122381070</v>
       </c>
       <c r="B5" t="n">
         <v>78651</v>
@@ -1041,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563283</v>
+        <v>563303</v>
       </c>
       <c r="R5" t="n">
-        <v>7041083</v>
+        <v>7041148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381436</v>
+        <v>122381396</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>79732</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563292</v>
+        <v>563278</v>
       </c>
       <c r="R6" t="n">
-        <v>7041070</v>
+        <v>7041093</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,12 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,12 +1223,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381405</v>
+        <v>122381436</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563283</v>
+        <v>563292</v>
       </c>
       <c r="R3" t="n">
-        <v>7041083</v>
+        <v>7041070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381436</v>
+        <v>122381396</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +910,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563292</v>
+        <v>563278</v>
       </c>
       <c r="R4" t="n">
-        <v>7041070</v>
+        <v>7041093</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +989,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381070</v>
+        <v>122381405</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,11 +1019,6 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1051,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563303</v>
+        <v>563283</v>
       </c>
       <c r="R5" t="n">
-        <v>7041148</v>
+        <v>7041083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381396</v>
+        <v>122381070</v>
       </c>
       <c r="B6" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1124,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563278</v>
+        <v>563303</v>
       </c>
       <c r="R6" t="n">
-        <v>7041093</v>
+        <v>7041148</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381436</v>
+        <v>122381405</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563292</v>
+        <v>563283</v>
       </c>
       <c r="R3" t="n">
-        <v>7041070</v>
+        <v>7041083</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381396</v>
+        <v>122381070</v>
       </c>
       <c r="B4" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,16 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563278</v>
+        <v>563303</v>
       </c>
       <c r="R4" t="n">
-        <v>7041093</v>
+        <v>7041148</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381405</v>
+        <v>122381436</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,29 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563283</v>
+        <v>563292</v>
       </c>
       <c r="R5" t="n">
-        <v>7041083</v>
+        <v>7041070</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381070</v>
+        <v>122381396</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,16 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563303</v>
+        <v>563278</v>
       </c>
       <c r="R6" t="n">
-        <v>7041148</v>
+        <v>7041093</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381405</v>
+        <v>122381070</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563283</v>
+        <v>563303</v>
       </c>
       <c r="R3" t="n">
-        <v>7041083</v>
+        <v>7041148</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381070</v>
+        <v>122381436</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563303</v>
+        <v>563292</v>
       </c>
       <c r="R4" t="n">
-        <v>7041148</v>
+        <v>7041070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381436</v>
+        <v>122381396</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563292</v>
+        <v>563278</v>
       </c>
       <c r="R5" t="n">
-        <v>7041070</v>
+        <v>7041093</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381396</v>
+        <v>122381405</v>
       </c>
       <c r="B6" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563278</v>
+        <v>563283</v>
       </c>
       <c r="R6" t="n">
-        <v>7041093</v>
+        <v>7041083</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381070</v>
+        <v>122381396</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563303</v>
+        <v>563278</v>
       </c>
       <c r="R3" t="n">
-        <v>7041148</v>
+        <v>7041093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381396</v>
+        <v>122381070</v>
       </c>
       <c r="B5" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563278</v>
+        <v>563303</v>
       </c>
       <c r="R5" t="n">
-        <v>7041093</v>
+        <v>7041148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381436</v>
+        <v>122381405</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563292</v>
+        <v>563283</v>
       </c>
       <c r="R4" t="n">
-        <v>7041070</v>
+        <v>7041083</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +989,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381070</v>
+        <v>122381436</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563303</v>
+        <v>563292</v>
       </c>
       <c r="R5" t="n">
-        <v>7041148</v>
+        <v>7041070</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,19 +1111,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381405</v>
+        <v>122381070</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563283</v>
+        <v>563303</v>
       </c>
       <c r="R6" t="n">
-        <v>7041083</v>
+        <v>7041148</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381396</v>
+        <v>122381070</v>
       </c>
       <c r="B3" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563278</v>
+        <v>563303</v>
       </c>
       <c r="R3" t="n">
-        <v>7041093</v>
+        <v>7041148</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381405</v>
+        <v>122381436</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563283</v>
+        <v>563292</v>
       </c>
       <c r="R4" t="n">
-        <v>7041083</v>
+        <v>7041070</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381436</v>
+        <v>122381405</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563292</v>
+        <v>563283</v>
       </c>
       <c r="R5" t="n">
-        <v>7041070</v>
+        <v>7041083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381070</v>
+        <v>122381396</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563303</v>
+        <v>563278</v>
       </c>
       <c r="R6" t="n">
-        <v>7041148</v>
+        <v>7041093</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381070</v>
+        <v>122381436</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563303</v>
+        <v>563292</v>
       </c>
       <c r="R3" t="n">
-        <v>7041148</v>
+        <v>7041070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381436</v>
+        <v>122381405</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563292</v>
+        <v>563283</v>
       </c>
       <c r="R4" t="n">
-        <v>7041070</v>
+        <v>7041083</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381405</v>
+        <v>122381070</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563283</v>
+        <v>563303</v>
       </c>
       <c r="R5" t="n">
-        <v>7041083</v>
+        <v>7041148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>122381396</v>
       </c>
       <c r="B6" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381436</v>
+        <v>122381396</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563292</v>
+        <v>563278</v>
       </c>
       <c r="R3" t="n">
-        <v>7041070</v>
+        <v>7041093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1123,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381396</v>
+        <v>122381436</v>
       </c>
       <c r="B6" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1129,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flarmyran, Flarmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563278</v>
+        <v>563292</v>
       </c>
       <c r="R6" t="n">
-        <v>7041093</v>
+        <v>7041070</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,12 +1223,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>112354202</v>
       </c>
       <c r="B2" t="n">
-        <v>89594</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563292</v>
+        <v>563291</v>
       </c>
       <c r="R2" t="n">
         <v>7041149</v>
@@ -765,49 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381396</v>
+        <v>122381070</v>
       </c>
       <c r="B3" t="n">
-        <v>79741</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563278</v>
+        <v>563303</v>
       </c>
       <c r="R3" t="n">
-        <v>7041093</v>
+        <v>7041148</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,16 +882,11 @@
         <v>122381405</v>
       </c>
       <c r="B4" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1001,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381070</v>
+        <v>122381396</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563303</v>
+        <v>563278</v>
       </c>
       <c r="R5" t="n">
-        <v>7041148</v>
+        <v>7041093</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1096,7 @@
         <v>122381436</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57081-2024 artfynd.xlsx
+++ b/artfynd/A 57081-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354202</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122381070</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122381405</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122381396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,8 +1232,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122381436</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>